--- a/data/trans_bre/P2B_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P2B_R-Provincia-trans_bre.xlsx
@@ -602,7 +602,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -660,49 +660,49 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,61; 23,4</t>
+          <t>-9,2; 23,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 20,89</t>
+          <t>-4,75; 20,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-30,48; 0,03</t>
+          <t>-28,25; 2,08</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 34,93</t>
+          <t>-1,62; 31,59</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-16,15; 72,89</t>
+          <t>-18,4; 73,02</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 28,56</t>
+          <t>-5,23; 27,41</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-37,04; 0,06</t>
+          <t>-34,9; 2,89</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-20,36; 592,78</t>
+          <t>-24,98; 544,0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -760,49 +760,49 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 21,38</t>
+          <t>-1,57; 21,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-17,2; 7,6</t>
+          <t>-19,21; 6,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-18,95; 8,28</t>
+          <t>-18,48; 9,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-17,28; 3,18</t>
+          <t>-17,48; 2,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-9,83; 141,78</t>
+          <t>-8,18; 148,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-20,25; 10,24</t>
+          <t>-22,64; 8,87</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-43,06; 25,76</t>
+          <t>-41,07; 28,5</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-69,48; 14,84</t>
+          <t>-68,34; 12,83</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,99; 17,38</t>
+          <t>-9,2; 16,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,32; 17,39</t>
+          <t>-8,69; 16,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,56; 22,55</t>
+          <t>-9,15; 21,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,16; 10,63</t>
+          <t>-10,54; 9,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-26,95; 87,31</t>
+          <t>-29,74; 80,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-11,28; 25,71</t>
+          <t>-10,45; 23,88</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-19,04; 78,06</t>
+          <t>-19,91; 70,08</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-48,37; 88,24</t>
+          <t>-48,91; 79,93</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-11,1; 13,85</t>
+          <t>-12,26; 13,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 6,31</t>
+          <t>-3,85; 5,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-19,98; 9,89</t>
+          <t>-20,08; 8,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-39,52; -0,3</t>
+          <t>-43,08; -1,86</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-31,8; 57,9</t>
+          <t>-34,38; 59,4</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 6,95</t>
+          <t>-3,86; 6,3</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-22,68; 13,74</t>
+          <t>-23,3; 12,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-59,79; -0,42</t>
+          <t>-63,06; -2,16</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-29,97; 35,81</t>
+          <t>-29,42; 37,1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-29,0; 7,38</t>
+          <t>-27,97; 8,34</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,05; 3,52</t>
+          <t>-5,89; 3,54</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-25,44; 8,07</t>
+          <t>-24,63; 8,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-69,14; 239,7</t>
+          <t>-69,31; 310,16</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-31,39; 8,04</t>
+          <t>-29,68; 8,98</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,19; 3,65</t>
+          <t>-5,91; 3,67</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-61,84; 34,13</t>
+          <t>-59,61; 41,35</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1160,49 +1160,49 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-20,62; 5,62</t>
+          <t>-19,05; 8,57</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-22,94; 5,77</t>
+          <t>-23,48; 5,88</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-34,33; 6,13</t>
+          <t>-36,09; 4,53</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-22,27; 7,03</t>
+          <t>-22,22; 6,28</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-60,8; 27,32</t>
+          <t>-55,76; 44,82</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-27,3; 7,75</t>
+          <t>-27,46; 8,1</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-41,18; 9,6</t>
+          <t>-43,42; 6,34</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-47,31; 20,9</t>
+          <t>-46,93; 17,88</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-15,79; 4,14</t>
+          <t>-16,2; 3,35</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-10,94; 7,87</t>
+          <t>-10,89; 6,31</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-10,92; 10,78</t>
+          <t>-10,56; 10,16</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,18; 5,44</t>
+          <t>-5,31; 5,45</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-45,01; 17,16</t>
+          <t>-43,4; 15,15</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-13,62; 10,81</t>
+          <t>-13,57; 8,76</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-16,37; 19,82</t>
+          <t>-15,76; 18,26</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-51,7; 122,5</t>
+          <t>-51,85; 116,28</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-9,48; 13,96</t>
+          <t>-9,05; 13,4</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 7,49</t>
+          <t>-4,8; 7,42</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 8,03</t>
+          <t>-0,96; 8,05</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-8,92; 7,3</t>
+          <t>-9,42; 8,07</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-21,74; 47,67</t>
+          <t>-21,82; 44,43</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 8,65</t>
+          <t>-5,11; 8,6</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 9,1</t>
+          <t>-1,05; 8,99</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-10,69; 9,48</t>
+          <t>-10,89; 10,53</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 5,27</t>
+          <t>-3,61; 5,98</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,91; 2,61</t>
+          <t>-4,95; 2,55</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,43; 2,75</t>
+          <t>-6,14; 2,94</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-9,45; 1,95</t>
+          <t>-8,85; 1,72</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-11,9; 18,98</t>
+          <t>-10,71; 21,73</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-5,79; 3,13</t>
+          <t>-5,83; 3,13</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-8,95; 4,09</t>
+          <t>-8,56; 4,51</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-25,79; 6,15</t>
+          <t>-24,84; 5,18</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2B_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P2B_R-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,2; 23,95</t>
+          <t>-7,9; 24,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 20,51</t>
+          <t>-4,36; 20,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-28,25; 2,08</t>
+          <t>-30,48; 0,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 31,59</t>
+          <t>-0,78; 30,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-18,4; 73,02</t>
+          <t>-16,01; 78,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 27,41</t>
+          <t>-4,8; 28,33</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-34,9; 2,89</t>
+          <t>-36,85; 1,27</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-24,98; 544,0</t>
+          <t>-20,49; 521,25</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 21,95</t>
+          <t>-2,35; 21,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-19,21; 6,73</t>
+          <t>-18,04; 9,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-18,48; 9,01</t>
+          <t>-18,22; 7,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-17,48; 2,55</t>
+          <t>-18,21; 1,54</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 148,03</t>
+          <t>-8,47; 146,09</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-22,64; 8,87</t>
+          <t>-22,17; 12,15</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-41,07; 28,5</t>
+          <t>-39,8; 23,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-68,34; 12,83</t>
+          <t>-69,19; 6,42</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,2; 16,33</t>
+          <t>-7,52; 17,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,69; 16,71</t>
+          <t>-9,63; 16,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,15; 21,16</t>
+          <t>-8,71; 21,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,54; 9,65</t>
+          <t>-10,94; 10,7</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-29,74; 80,9</t>
+          <t>-25,38; 91,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-10,45; 23,88</t>
+          <t>-11,84; 25,04</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-19,91; 70,08</t>
+          <t>-20,14; 69,53</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-48,91; 79,93</t>
+          <t>-50,17; 85,57</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-12,26; 13,96</t>
+          <t>-11,99; 13,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 5,84</t>
+          <t>-4,03; 6,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-20,08; 8,67</t>
+          <t>-18,84; 10,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-43,08; -1,86</t>
+          <t>-41,37; -1,6</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-34,38; 59,4</t>
+          <t>-33,58; 59,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 6,3</t>
+          <t>-4,01; 7,16</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-23,3; 12,07</t>
+          <t>-21,77; 14,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-63,06; -2,16</t>
+          <t>-62,38; -4,53</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-29,42; 37,1</t>
+          <t>-30,68; 36,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-27,97; 8,34</t>
+          <t>-29,98; 6,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 3,54</t>
+          <t>-6,0; 3,5</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-24,63; 8,43</t>
+          <t>-24,66; 7,37</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-69,31; 310,16</t>
+          <t>-71,08; 231,5</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-29,68; 8,98</t>
+          <t>-31,66; 7,28</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,91; 3,67</t>
+          <t>-6,0; 3,63</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-59,61; 41,35</t>
+          <t>-60,21; 28,48</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-19,05; 8,57</t>
+          <t>-19,62; 7,57</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-23,48; 5,88</t>
+          <t>-22,75; 6,4</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-36,09; 4,53</t>
+          <t>-35,73; 5,57</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-22,22; 6,28</t>
+          <t>-24,1; 6,46</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-55,76; 44,82</t>
+          <t>-58,48; 36,47</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-27,46; 8,1</t>
+          <t>-26,84; 8,4</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-43,42; 6,34</t>
+          <t>-43,42; 7,04</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-46,93; 17,88</t>
+          <t>-49,27; 18,66</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-16,2; 3,35</t>
+          <t>-15,95; 3,9</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-10,89; 6,31</t>
+          <t>-10,67; 7,07</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-10,56; 10,16</t>
+          <t>-10,52; 9,61</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 5,45</t>
+          <t>-5,58; 5,71</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-43,4; 15,15</t>
+          <t>-46,93; 14,04</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-13,57; 8,76</t>
+          <t>-13,15; 9,74</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-15,76; 18,26</t>
+          <t>-15,67; 16,88</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-51,85; 116,28</t>
+          <t>-56,05; 126,68</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-9,05; 13,4</t>
+          <t>-8,97; 13,89</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-4,8; 7,42</t>
+          <t>-5,57; 7,35</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 8,05</t>
+          <t>-1,54; 8,18</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-9,42; 8,07</t>
+          <t>-8,97; 7,46</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-21,82; 44,43</t>
+          <t>-21,11; 43,65</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 8,6</t>
+          <t>-6,03; 8,57</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 8,99</t>
+          <t>-1,62; 9,21</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-10,89; 10,53</t>
+          <t>-10,5; 9,62</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 5,98</t>
+          <t>-2,73; 6,0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 2,55</t>
+          <t>-4,89; 2,97</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,14; 2,94</t>
+          <t>-6,41; 3,07</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-8,85; 1,72</t>
+          <t>-8,76; 1,48</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-10,71; 21,73</t>
+          <t>-8,18; 21,65</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 3,13</t>
+          <t>-5,7; 3,7</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-8,56; 4,51</t>
+          <t>-9,01; 4,61</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-24,84; 5,18</t>
+          <t>-23,91; 4,58</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2B_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P2B_R-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10,56</t>
+          <t>3,33</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>113,71%</t>
+          <t>34,3%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,9; 24,47</t>
+          <t>-7,61; 23,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 20,76</t>
+          <t>-5,64; 20,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-30,48; 0,89</t>
+          <t>-30,48; 0,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 30,06</t>
+          <t>-5,28; 13,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-16,01; 78,06</t>
+          <t>-16,15; 72,89</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,8; 28,33</t>
+          <t>-5,51; 28,56</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-36,85; 1,27</t>
+          <t>-37,04; 0,06</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-20,49; 521,25</t>
+          <t>-42,71; 236,01</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-7,23</t>
+          <t>-3,31</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-33,71%</t>
+          <t>-15,9%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 21,36</t>
+          <t>-2,31; 21,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-18,04; 9,2</t>
+          <t>-17,2; 7,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-18,22; 7,24</t>
+          <t>-18,95; 8,28</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-18,21; 1,54</t>
+          <t>-11,84; 6,17</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-8,47; 146,09</t>
+          <t>-9,83; 141,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-22,17; 12,15</t>
+          <t>-20,25; 10,24</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-39,8; 23,26</t>
+          <t>-43,06; 25,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-69,19; 6,42</t>
+          <t>-47,42; 36,32</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,27</t>
+          <t>0,16</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-1,6%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,52; 17,14</t>
+          <t>-7,99; 17,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,63; 16,74</t>
+          <t>-9,32; 17,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,71; 21,1</t>
+          <t>-8,56; 22,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,94; 10,7</t>
+          <t>-9,51; 10,97</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-25,38; 91,52</t>
+          <t>-26,95; 87,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-11,84; 25,04</t>
+          <t>-11,28; 25,71</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-20,14; 69,53</t>
+          <t>-19,04; 78,06</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-50,17; 85,57</t>
+          <t>-46,22; 97,68</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-17,58</t>
+          <t>-16,92</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-34,14%</t>
+          <t>-33,4%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-11,99; 13,53</t>
+          <t>-11,1; 13,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 6,23</t>
+          <t>-3,93; 6,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-18,84; 10,42</t>
+          <t>-19,98; 9,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-41,37; -1,6</t>
+          <t>-36,82; 0,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-33,58; 59,56</t>
+          <t>-31,8; 57,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 7,16</t>
+          <t>-4,0; 6,95</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-21,77; 14,02</t>
+          <t>-22,68; 13,74</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-62,38; -4,53</t>
+          <t>-57,21; 5,26</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-8,62</t>
+          <t>-5,87</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-25,81%</t>
+          <t>-18,75%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-30,68; 36,76</t>
+          <t>-29,97; 35,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-29,98; 6,46</t>
+          <t>-29,0; 7,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,0; 3,5</t>
+          <t>-6,05; 3,52</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-24,66; 7,37</t>
+          <t>-22,55; 9,92</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-71,08; 231,5</t>
+          <t>-69,14; 239,7</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-31,66; 7,28</t>
+          <t>-31,39; 8,04</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,0; 3,63</t>
+          <t>-6,19; 3,65</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-60,21; 28,48</t>
+          <t>-58,53; 43,96</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-9,21</t>
+          <t>-10,2</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-22,24%</t>
+          <t>-25,66%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-19,62; 7,57</t>
+          <t>-20,62; 5,62</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-22,75; 6,4</t>
+          <t>-22,94; 5,77</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-35,73; 5,57</t>
+          <t>-34,33; 6,13</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-24,1; 6,46</t>
+          <t>-23,23; 5,57</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-58,48; 36,47</t>
+          <t>-60,8; 27,32</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-26,84; 8,4</t>
+          <t>-27,3; 7,75</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-43,42; 7,04</t>
+          <t>-41,18; 9,6</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-49,27; 18,66</t>
+          <t>-49,58; 18,71</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,19</t>
+          <t>0,48</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>6,51%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-15,95; 3,9</t>
+          <t>-15,79; 4,14</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-10,67; 7,07</t>
+          <t>-10,94; 7,87</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-10,52; 9,61</t>
+          <t>-10,92; 10,78</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 5,71</t>
+          <t>-5,13; 5,86</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-46,93; 14,04</t>
+          <t>-45,01; 17,16</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-13,15; 9,74</t>
+          <t>-13,62; 10,81</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-15,67; 16,88</t>
+          <t>-16,37; 19,82</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-56,05; 126,68</t>
+          <t>-50,63; 127,71</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-0,79</t>
+          <t>-1,64</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-0,97%</t>
+          <t>-2,03%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-8,97; 13,89</t>
+          <t>-9,48; 13,96</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 7,35</t>
+          <t>-4,66; 7,49</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 8,18</t>
+          <t>-1,04; 8,03</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-8,97; 7,46</t>
+          <t>-10,5; 7,03</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-21,11; 43,65</t>
+          <t>-21,74; 47,67</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 8,57</t>
+          <t>-5,11; 8,65</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 9,21</t>
+          <t>-1,04; 9,1</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-10,5; 9,62</t>
+          <t>-12,73; 9,06</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-3,54</t>
+          <t>-3,23</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>-10,31%</t>
+          <t>-9,11%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 6,0</t>
+          <t>-4,05; 5,27</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 2,97</t>
+          <t>-4,91; 2,61</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,41; 3,07</t>
+          <t>-6,43; 2,75</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-8,76; 1,48</t>
+          <t>-8,6; 1,67</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 21,65</t>
+          <t>-11,9; 18,98</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 3,7</t>
+          <t>-5,79; 3,13</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-9,01; 4,61</t>
+          <t>-8,95; 4,09</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-23,91; 4,58</t>
+          <t>-22,56; 4,96</t>
         </is>
       </c>
     </row>
